--- a/data/trans_dic/IP25B_1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP25B_1_R-Provincia-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,51; 27,48</t>
+          <t>7,25; 26,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,72; 23,07</t>
+          <t>7,83; 22,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,81; 20,11</t>
+          <t>9,01; 20,4</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,49; 72,98</t>
+          <t>32,01; 73,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,72; 48,06</t>
+          <t>30,22; 48,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,07; 62,57</t>
+          <t>34,82; 61,64</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,58; 35,12</t>
+          <t>17,03; 34,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,31; 31,73</t>
+          <t>13,54; 30,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,52; 30,56</t>
+          <t>17,75; 30,61</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,23; 26,75</t>
+          <t>9,69; 26,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,53; 58,37</t>
+          <t>17,41; 58,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,19; 41,87</t>
+          <t>16,34; 42,96</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,7</t>
+          <t>0,0; 8,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,9; 34,12</t>
+          <t>10,14; 34,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,28; 20,37</t>
+          <t>5,73; 20,26</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19,16; 39,56</t>
+          <t>18,33; 39,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,1; 30,97</t>
+          <t>12,46; 29,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,23; 30,57</t>
+          <t>17,36; 30,38</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,59; 34,16</t>
+          <t>21,12; 34,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24,47; 41,84</t>
+          <t>24,85; 42,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24,82; 37,53</t>
+          <t>24,85; 36,71</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,87; 20,88</t>
+          <t>9,2; 19,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,85; 15,15</t>
+          <t>6,66; 15,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,58; 15,72</t>
+          <t>8,8; 15,86</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20,3; 35,17</t>
+          <t>20,23; 35,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20,71; 28,44</t>
+          <t>20,88; 28,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21,7; 29,93</t>
+          <t>21,82; 29,72</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5471; 20008</t>
+          <t>5278; 19412</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6123; 18308</t>
+          <t>6218; 18150</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13411; 30606</t>
+          <t>13718; 31038</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40687; 91392</t>
+          <t>40090; 92433</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37696; 60952</t>
+          <t>38334; 61844</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88407; 157720</t>
+          <t>87758; 155368</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10174; 20327</t>
+          <t>9855; 19991</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9608; 21311</t>
+          <t>9091; 20680</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21905; 38213</t>
+          <t>22190; 38268</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5977; 17327</t>
+          <t>6274; 17257</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12501; 44133</t>
+          <t>13167; 44187</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21330; 58778</t>
+          <t>22933; 60302</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2659</t>
+          <t>0; 2855</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4029; 13895</t>
+          <t>4130; 13923</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4725; 15327</t>
+          <t>4314; 15241</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8848; 18265</t>
+          <t>8464; 18446</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6796; 17398</t>
+          <t>7002; 16333</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17635; 31290</t>
+          <t>17764; 31094</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>24544; 40726</t>
+          <t>25184; 41489</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>37384; 63912</t>
+          <t>37964; 65182</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>67501; 102072</t>
+          <t>67573; 99847</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>11564; 27227</t>
+          <t>12003; 26022</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>10715; 23705</t>
+          <t>10413; 24003</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>24607; 45104</t>
+          <t>25233; 45487</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>132180; 228954</t>
+          <t>131679; 231542</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>156383; 214708</t>
+          <t>157692; 216130</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>305178; 420889</t>
+          <t>306744; 417915</t>
         </is>
       </c>
     </row>
